--- a/docs/oc-regiones/suministro-de-combustibles/antofagasta.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M245"/>
+  <dimension ref="A1:M247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>36336.53</v>
+        <v>36028.78</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.78</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9084.129999999999</v>
+        <v>8993.469999999999</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17099.54</v>
+        <v>16928.89</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21374.43</v>
+        <v>21136.29</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>42748.86</v>
+        <v>42514.75</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>32061.64</v>
+        <v>31886.06</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>32061.64</v>
+        <v>32176.07</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>64123.29</v>
+        <v>64352.13</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16030.82</v>
+        <v>16088.03</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4274.89</v>
+        <v>4321.38</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3206.16</v>
+        <v>3241.04</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8122.28</v>
+        <v>8210.620000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5471.85</v>
+        <v>5489.85</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4916.12</v>
+        <v>4932.29</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3740.53</v>
+        <v>3805.09</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3740.53</v>
+        <v>3805.09</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3206.16</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>37405.25</v>
+        <v>37664.38</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10687.21</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5877.97</v>
+        <v>5905.34</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18892.3</v>
+        <v>18858.79</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2229.63</v>
+        <v>2220.44</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2521.17</v>
+        <v>2510.78</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4274.89</v>
+        <v>4257.27</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3206.16</v>
+        <v>3201.2</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3206.16</v>
+        <v>3228.79</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>17464.14</v>
+        <v>17238.41</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2292.17</v>
+        <v>2262.54</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>27287.72</v>
+        <v>26941.11</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3383.68</v>
+        <v>3340.7</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2292.17</v>
+        <v>2269.36</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4256.88</v>
+        <v>4214.53</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4366.04</v>
+        <v>4350.38</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2292.17</v>
+        <v>2283.95</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10915.09</v>
+        <v>10875.95</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5948.72</v>
+        <v>5935.85</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3410.46</v>
+        <v>3381.57</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6147.96</v>
+        <v>6143.01</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2281.25</v>
+        <v>2290.01</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>9823.309999999999</v>
+        <v>9809.530000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5457.54</v>
+        <v>5449.89</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>36019.79</v>
+        <v>36065.97</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5457.54</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>24013.19</v>
+        <v>24178.48</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>11114.72</v>
+        <v>11191.22</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2624.21</v>
+        <v>2646.64</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17027.54</v>
+        <v>17210.18</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3618.77</v>
+        <v>3657.58</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>10915.09</v>
+        <v>11032.17</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3274.53</v>
+        <v>3309.65</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2292.17</v>
+        <v>2321.62</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8732.07</v>
+        <v>8844.27</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8732.07</v>
+        <v>8844.27</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3383.68</v>
+        <v>3402.18</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2277.98</v>
+        <v>2290.44</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2292.17</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4256.88</v>
+        <v>4280.16</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>21830.18</v>
+        <v>21949.56</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3003.08</v>
+        <v>3019.5</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2292.17</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>40725.56</v>
+        <v>39772.85</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>20362.78</v>
+        <v>19886.43</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8196.02</v>
+        <v>8078.54</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5656.33</v>
+        <v>5584.53</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3393.8</v>
+        <v>3350.72</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>39028.66</v>
+        <v>38466.26</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>18100.01</v>
+        <v>17839.19</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>38463.03</v>
+        <v>37965.92</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8196.02</v>
+        <v>8179.88</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>6335.09</v>
+        <v>6330.76</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>11312.66</v>
+        <v>11241.77</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2375.66</v>
+        <v>2360.77</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5656.33</v>
+        <v>5693.4</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2375.66</v>
+        <v>2391.23</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>33937.97</v>
+        <v>34394.99</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>16376.2</v>
+        <v>16596.73</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>13575.19</v>
+        <v>13758</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5656.33</v>
+        <v>5732.5</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3393.8</v>
+        <v>3445.46</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2375.66</v>
+        <v>2411.82</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3393.8</v>
+        <v>3476.33</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>11312.66</v>
+        <v>11587.75</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11312.66</v>
+        <v>11655.69</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>39028.66</v>
+        <v>40212.13</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3393.8</v>
+        <v>3494.67</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2436.14</v>
+        <v>2425.87</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>20881.19</v>
+        <v>20793.14</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2436.14</v>
+        <v>2425.87</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4524.26</v>
+        <v>4505.18</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>17400.99</v>
+        <v>17559.26</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>34801.98</v>
+        <v>35118.53</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2900.16</v>
+        <v>2920.36</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>23201.32</v>
+        <v>23362.85</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>18560.39</v>
+        <v>18682.62</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8136.7</v>
+        <v>8209.17</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3480.2</v>
+        <v>3474.23</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>8136.7</v>
+        <v>8124.73</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>25521.45</v>
+        <v>25382.47</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>10317.63</v>
+        <v>10256.82</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3248.18</v>
+        <v>3228.45</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>7716.29</v>
+        <v>8057.06</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>19782.54</v>
+        <v>20357.15</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3297.09</v>
+        <v>3305.2</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>7862.46</v>
+        <v>7806.98</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5495.15</v>
+        <v>5594.78</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>13203.75</v>
+        <v>13410.58</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4396.12</v>
+        <v>4399.91</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2307.96</v>
+        <v>2317.5</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7877.85</v>
+        <v>7856.12</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2307.96</v>
+        <v>2301.6</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>17584.45</v>
+        <v>17535.94</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>7693.21</v>
+        <v>7604.4</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>10990.3</v>
+        <v>10927.17</v>
       </c>
     </row>
     <row r="124">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3846.61</v>
+        <v>3824.51</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>650-23-CM26</t>
+          <t>1747-56-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.606.205-0</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>HOSPITAL DE MEJILLONES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2304.67</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1747-56-CM26</t>
+          <t>650-23-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.606.205-0</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HOSPITAL DE MEJILLONES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2307.96</v>
+        <v>2291.43</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.89</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4396.12</v>
+        <v>4332.52</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>71436.96000000001</v>
+        <v>69774.67999999999</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2784.32</v>
+        <v>2695.53</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>5568.63</v>
+        <v>5391.07</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4454.91</v>
+        <v>4367.05</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2338.83</v>
+        <v>2277.24</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4521.73</v>
+        <v>4402.66</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>5568.63</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>23945.13</v>
+        <v>23314.57</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3675.3</v>
+        <v>3578.52</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2672.94</v>
+        <v>2601.37</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3341.18</v>
+        <v>3350.91</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.42</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>12528.31</v>
+        <v>12580.38</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4454.91</v>
+        <v>4473.42</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3341.18</v>
+        <v>3369.54</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2993.03</v>
+        <v>3018.43</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>26729.45</v>
+        <v>27058.41</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12528.31</v>
+        <v>12695.1</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>14798.86</v>
+        <v>14995.87</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>6125.5</v>
+        <v>6207.04</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>7350.6</v>
+        <v>7446.52</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>5568.63</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>37866.71</v>
+        <v>38798.61</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3675.3</v>
+        <v>3708.41</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2338.83</v>
+        <v>2359.9</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2358.87</v>
+        <v>2380.12</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>12793.38</v>
+        <v>12908.63</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3341.18</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>44549.08</v>
+        <v>44689.24</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>13364.72</v>
+        <v>13406.77</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2450.2</v>
+        <v>2460.35</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>7796.09</v>
+        <v>7812.24</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>22273.81</v>
+        <v>22178.13</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>23951.75</v>
+        <v>23808.21</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>12796.92</v>
+        <v>12622.94</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>5639.47</v>
+        <v>5562.8</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>12796.92</v>
+        <v>12687.77</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>6684.21</v>
+        <v>6720.2</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4456.14</v>
+        <v>4473.02</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>12430.4</v>
+        <v>12477.5</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3676.32</v>
+        <v>3667.03</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>22889.91</v>
+        <v>22832.12</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>11140.35</v>
+        <v>11112.22</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>55701.75</v>
+        <v>55146.25</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>3899.12</v>
+        <v>3882.03</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>5570.17</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2450.88</v>
+        <v>2440.13</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5570.17</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>12430.4</v>
+        <v>12295.18</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>12430.4</v>
+        <v>12491.46</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2785.09</v>
+        <v>2794.33</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3676.32</v>
+        <v>3688.51</v>
       </c>
     </row>
     <row r="183">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3139.28</v>
+        <v>3149.27</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1057385-157-CM26</t>
+          <t>3834-150-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>5570.17</v>
+        <v>26879.01</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3834-150-CM26</t>
+          <t>1057385-157-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>26736.84</v>
+        <v>5599.79</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>71951.66</v>
+        <v>72981.23</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>11855.42</v>
+        <v>11994.49</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>16604.23</v>
+        <v>16799.01</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>23799.4</v>
+        <v>24078.57</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2948.91</v>
+        <v>2983.5</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>6641.69</v>
+        <v>6719.6</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>16604.23</v>
+        <v>16885.05</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5534.74</v>
+        <v>5586.65</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>17710.36</v>
+        <v>17576.01</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>27673.72</v>
+        <v>27463.78</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>11901.91</v>
+        <v>11700.82</v>
       </c>
     </row>
     <row r="198">
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>5534.74</v>
+        <v>5441.23</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1113265-55-CM26</t>
+          <t>4051-116-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12556,12 +12556,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2374.6</v>
+        <v>11738.38</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4051-116-CM26</t>
+          <t>1113265-55-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>11901.91</v>
+        <v>2341.98</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>7748.64</v>
+        <v>7700.6</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>3652.93</v>
+        <v>3669.52</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5534.74</v>
+        <v>5617.16</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>11901.91</v>
+        <v>12128.19</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>66416.92</v>
+        <v>67679.60000000001</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2374.6</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>6641.69</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2374.6</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2656.68</v>
+        <v>2664.89</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>11003.07</v>
+        <v>10973.97</v>
       </c>
     </row>
     <row r="211">
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2435.29</v>
+        <v>2402.85</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4468-93-CM26</t>
+          <t>1401-29-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13344,17 +13344,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>39576.51</v>
+        <v>4573.65</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1747-125-CM26</t>
+          <t>1775-38-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.606.205-0</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>HOSPITAL DE MEJILLONES</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2374.6</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1401-29-CM26</t>
+          <t>1747-125-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.205-0</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL DE MEJILLONES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>4664.96</v>
+        <v>2328.12</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1775-38-CM26</t>
+          <t>4468-93-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13527,17 +13527,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>11069.49</v>
+        <v>38801.85</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1158-72-CM26</t>
+          <t>1057384-522-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13588,17 +13588,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>5601.16</v>
+        <v>6543.29</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3506-472-CM26</t>
+          <t>3506-473-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>23799.4</v>
+        <v>3598.81</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3506-473-CM26</t>
+          <t>3506-472-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3652.93</v>
+        <v>23446.79</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1057384-522-CM26</t>
+          <t>1158-72-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13771,17 +13771,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>6641.69</v>
+        <v>5518.17</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>10669.52</v>
+        <v>10770.87</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3222.45</v>
+        <v>3253.06</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3222.45</v>
+        <v>3253.06</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2685.37</v>
+        <v>2710.88</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>18259.45</v>
+        <v>18432.89</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.71</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>8626.73</v>
       </c>
     </row>
     <row r="227">
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>10677.04</v>
+        <v>10784.42</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>697036-44-CM26</t>
+          <t>1230848-139-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2309.42</v>
+        <v>7594.33</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1230848-139-CM26</t>
+          <t>697036-44-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7519.04</v>
+        <v>2332.54</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>32224.45</v>
+        <v>32388.66</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>6444.89</v>
+        <v>6477.73</v>
       </c>
     </row>
     <row r="232">
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>10677.04</v>
+        <v>10718.6</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2215-765-CM26</t>
+          <t>4999-24-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>10741.48</v>
+        <v>37675.32</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4999-24-CM26</t>
+          <t>2215-765-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>37595.2</v>
+        <v>10764.38</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>13587.98</v>
+        <v>13676.56</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>16112.23</v>
+        <v>16149.18</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>3544.69</v>
+        <v>3552.82</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3007.62</v>
+        <v>3027.75</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>7472.1</v>
+        <v>7524.39</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>10741.48</v>
+        <v>10719.95</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>18259.83</v>
+        <v>17965.16</v>
       </c>
     </row>
     <row r="242">
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2363.13</v>
+        <v>2325.24</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1346284-130-CM26</t>
+          <t>1158-100-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15235,17 +15235,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2309.42</v>
+        <v>10664.27</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1158-100-CM26</t>
+          <t>1346284-130-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15296,17 +15296,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>10789.82</v>
+        <v>2282.55</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,129 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2309.42</v>
+        <v>2324.88</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1410-711-CM26</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>5406.05</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2258-6867-CM26</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="n">
+        <v>6775.07</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/antofagasta.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/antofagasta.xlsx
@@ -562,7 +562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +24027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +24092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +24157,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +24222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24612,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24677,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24742,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24807,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +25002,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +25067,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +25197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +26042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +26107,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +26172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +26237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +26302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26692,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +27017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +27147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +27212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +27277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27732,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27797,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +28057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +28122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +28187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +28252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +28317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28447,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +29032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +29097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +29162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +29227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +29292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +30007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +30072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +30137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +30202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +30267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +30332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30397,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +31047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +31112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +31177,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +31242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +31307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +31372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31567,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31697,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +32022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +32087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +32152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +32217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +32282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +32347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +32412,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32672,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +33062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +33127,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +33192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +33257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +33322,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +33387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +33452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +33517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33647,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33972,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +34037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +34102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +34167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +34232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +34297,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +34362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +34427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +34492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +35012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +35077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +35142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +35207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +35272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +35337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/suministro-de-combustibles/antofagasta.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M537"/>
+  <dimension ref="A1:M562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2269,7 +2269,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4051-29-CM25</t>
+          <t>1233623-26-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2289,17 +2289,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7972.38</v>
+        <v>15502.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1233623-26-CM25</t>
+          <t>4051-29-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15502.43</v>
+        <v>7972.38</v>
       </c>
     </row>
     <row r="31">
@@ -2529,7 +2529,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4051-51-CM25</t>
+          <t>1410-191-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2549,17 +2549,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8202.950000000001</v>
+        <v>5321.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1410-191-CM25</t>
+          <t>4051-51-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2614,17 +2614,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5321.75</v>
+        <v>8202.950000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1216060-18-CM25</t>
+          <t>712-5-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.109.282-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes y Recreación Calama</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2122.34</v>
+        <v>2121.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>712-5-CM25</t>
+          <t>1216060-18-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>65.109.282-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Corporación Municipal de Deportes y Recreación Calama</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2121.1</v>
+        <v>2122.34</v>
       </c>
     </row>
     <row r="37">
@@ -3244,7 +3244,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1230848-22-CM25</t>
+          <t>1230848-23-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2619.94</v>
+        <v>3667.92</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1230848-23-CM25</t>
+          <t>1230848-22-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3667.92</v>
+        <v>2619.94</v>
       </c>
     </row>
     <row r="46">
@@ -3504,7 +3504,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>769-4260-CM25</t>
+          <t>4051-71-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>43172.3</v>
+        <v>8325.780000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4051-71-CM25</t>
+          <t>769-4260-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8325.780000000001</v>
+        <v>43172.3</v>
       </c>
     </row>
     <row r="50">
@@ -4089,7 +4089,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4468-52-CM25</t>
+          <t>1033-32-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4109,17 +4109,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>21456</v>
+        <v>18187.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1033-32-CM25</t>
+          <t>4468-52-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4174,17 +4174,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>18187.18</v>
+        <v>21456</v>
       </c>
     </row>
     <row r="59">
@@ -4414,7 +4414,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1410-346-CM25</t>
+          <t>697036-23-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5971.9</v>
+        <v>2714.5</v>
       </c>
     </row>
     <row r="63">
@@ -4544,7 +4544,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>697036-23-CM25</t>
+          <t>1410-346-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2714.5</v>
+        <v>5971.9</v>
       </c>
     </row>
     <row r="65">
@@ -4674,7 +4674,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4051-102-CM25</t>
+          <t>1057385-133-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4714,17 +4714,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>7924.92</v>
+        <v>4196.96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057385-133-CM25</t>
+          <t>4051-102-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4779,17 +4779,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4196.96</v>
+        <v>7924.92</v>
       </c>
     </row>
     <row r="68">
@@ -4934,7 +4934,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1230848-58-CM25</t>
+          <t>1230848-59-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2561.95</v>
+        <v>3586.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1573-31-CM25</t>
+          <t>1230848-58-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2152.04</v>
+        <v>2561.95</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1230848-59-CM25</t>
+          <t>1573-31-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3586.73</v>
+        <v>2152.04</v>
       </c>
     </row>
     <row r="73">
@@ -5194,7 +5194,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4051-111-CM25</t>
+          <t>3506-276-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7458.57</v>
+        <v>2112.91</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3506-276-CM25</t>
+          <t>664-31-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.402.017-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2112.91</v>
+        <v>3376.63</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>664-31-CM25</t>
+          <t>4051-111-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.402.017-2</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3376.63</v>
+        <v>7458.57</v>
       </c>
     </row>
     <row r="77">
@@ -5714,7 +5714,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1694-12-CM25</t>
+          <t>1694-11-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4952.38</v>
+        <v>2579.37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1694-11-CM25</t>
+          <t>1694-12-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2579.37</v>
+        <v>4952.38</v>
       </c>
     </row>
     <row r="84">
@@ -6169,7 +6169,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4051-137-CM25</t>
+          <t>769-4420-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7844.87</v>
+        <v>42652.56</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>769-4420-CM25</t>
+          <t>4051-137-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>42652.56</v>
+        <v>7844.87</v>
       </c>
     </row>
     <row r="91">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2385-319-CM25</t>
+          <t>4051-143-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6469,17 +6469,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>20927.73</v>
+        <v>7698.26</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4051-143-CM25</t>
+          <t>2385-319-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6534,17 +6534,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7698.26</v>
+        <v>20927.73</v>
       </c>
     </row>
     <row r="95">
@@ -7404,7 +7404,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3506-370-CM25</t>
+          <t>2429-2024-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7444,17 +7444,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2241.94</v>
+        <v>26689.73</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2429-2024-CM25</t>
+          <t>3506-370-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7509,17 +7509,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>26689.73</v>
+        <v>2241.94</v>
       </c>
     </row>
     <row r="110">
@@ -7664,7 +7664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1375735-35-CM25</t>
+          <t>3146-35-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7684,17 +7684,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>10629.14</v>
+        <v>3188.74</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3146-35-CM25</t>
+          <t>1375735-35-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7749,17 +7749,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3188.74</v>
+        <v>10629.14</v>
       </c>
     </row>
     <row r="114">
@@ -7859,7 +7859,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4051-180-CM25</t>
+          <t>2385-415-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7899,17 +7899,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7758.94</v>
+        <v>35738.29</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2385-415-CM25</t>
+          <t>4051-180-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7964,17 +7964,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>35738.29</v>
+        <v>7758.94</v>
       </c>
     </row>
     <row r="117">
@@ -8639,7 +8639,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1410-616-CM25</t>
+          <t>4051-195-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8659,17 +8659,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,13 +8698,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>5589.9</v>
+        <v>7728.03</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4051-195-CM25</t>
+          <t>1410-616-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8724,17 +8724,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>7728.03</v>
+        <v>5589.9</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4051-198-CM25</t>
+          <t>1288419-13-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>7687.04</v>
+        <v>53463.93</v>
       </c>
     </row>
     <row r="130">
@@ -8899,7 +8899,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1288419-13-CM25</t>
+          <t>4051-198-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>53463.93</v>
+        <v>7687.04</v>
       </c>
     </row>
     <row r="132">
@@ -9614,7 +9614,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2385-512-CM25</t>
+          <t>4051-218-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9654,17 +9654,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>36152.9</v>
+        <v>7901.84</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3506-479-CM25</t>
+          <t>2385-512-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9719,17 +9719,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>18346.25</v>
+        <v>36152.9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1057384-465-CM25</t>
+          <t>3506-479-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9764,17 +9764,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3237.57</v>
+        <v>18346.25</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4051-218-CM25</t>
+          <t>1057384-465-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9829,17 +9829,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>7901.84</v>
+        <v>3237.57</v>
       </c>
     </row>
     <row r="146">
@@ -10199,7 +10199,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3506-504-CM25</t>
+          <t>838098-50-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10219,17 +10219,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10239,17 +10239,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -10264,7 +10264,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>838098-50-CM25</t>
+          <t>3506-504-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10284,17 +10284,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -10329,7 +10329,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4051-231-CM25</t>
+          <t>2122-197-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10349,17 +10349,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>7703.88</v>
+        <v>5260.78</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2122-197-CM25</t>
+          <t>4051-231-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10414,17 +10414,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>5260.78</v>
+        <v>7703.88</v>
       </c>
     </row>
     <row r="155">
@@ -10654,7 +10654,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1230848-155-CM25</t>
+          <t>5601-34-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10674,17 +10674,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10713,13 +10713,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3624.5</v>
+        <v>2588.93</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1230848-156-CM25</t>
+          <t>712-24-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2588.93</v>
+        <v>3106.72</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>712-24-CM25</t>
+          <t>1230848-155-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10843,13 +10843,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3106.72</v>
+        <v>3624.5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5601-34-CM25</t>
+          <t>1230848-156-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10869,17 +10869,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -11239,7 +11239,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3916-363-CM25</t>
+          <t>4051-251-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11259,17 +11259,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>61849.93</v>
+        <v>7692.07</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4051-251-CM25</t>
+          <t>3916-363-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11324,17 +11324,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11363,7 +11363,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>7692.07</v>
+        <v>61849.93</v>
       </c>
     </row>
     <row r="169">
@@ -12019,7 +12019,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1230848-207-CM25</t>
+          <t>2215-1405-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12044,12 +12044,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2599.18</v>
+        <v>5198.37</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1230848-208-CM25</t>
+          <t>3834-194-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3638.86</v>
+        <v>22872.83</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3834-194-CM25</t>
+          <t>1230848-207-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>22872.83</v>
+        <v>2599.18</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2215-1405-CM25</t>
+          <t>1230848-208-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>5198.37</v>
+        <v>3638.86</v>
       </c>
     </row>
     <row r="183">
@@ -13319,7 +13319,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1158-113-CM25</t>
+          <t>4999-168-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13378,13 +13378,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3956.17</v>
+        <v>71169.16</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4999-168-CM25</t>
+          <t>1158-113-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,7 +13443,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>71169.16</v>
+        <v>3956.17</v>
       </c>
     </row>
     <row r="201">
@@ -13579,7 +13579,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1230848-240-CM25</t>
+          <t>4051-312-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13599,17 +13599,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13638,7 +13638,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4100.34</v>
+        <v>7837.96</v>
       </c>
     </row>
     <row r="204">
@@ -13709,7 +13709,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4051-312-CM25</t>
+          <t>1230848-240-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13729,17 +13729,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>7837.96</v>
+        <v>4100.34</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1230848-241-CM25</t>
+          <t>838098-75-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13814,17 +13814,17 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13833,7 +13833,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2213.86</v>
+        <v>3268.08</v>
       </c>
     </row>
     <row r="207">
@@ -13904,7 +13904,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>838098-75-CM25</t>
+          <t>1230848-241-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13944,17 +13944,17 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13963,7 +13963,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>3268.08</v>
+        <v>2213.86</v>
       </c>
     </row>
     <row r="209">
@@ -14164,7 +14164,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>697036-85-CM25</t>
+          <t>2385-871-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14189,12 +14189,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14204,17 +14204,17 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -14223,13 +14223,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>3128.58</v>
+        <v>35457.29</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2385-871-CM25</t>
+          <t>4051-314-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14269,17 +14269,17 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>35457.29</v>
+        <v>7767.23</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4051-314-CM25</t>
+          <t>697036-85-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>7767.23</v>
+        <v>3128.58</v>
       </c>
     </row>
     <row r="215">
@@ -14749,7 +14749,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2385-929-CM25</t>
+          <t>4051-329-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14774,12 +14774,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14789,17 +14789,17 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14808,13 +14808,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>10399.23</v>
+        <v>7825.42</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4051-329-CM25</t>
+          <t>2385-929-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14854,17 +14854,17 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14873,7 +14873,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>7825.42</v>
+        <v>10399.23</v>
       </c>
     </row>
     <row r="223">
@@ -15074,7 +15074,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1230848-293-CM25</t>
+          <t>1230848-292-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>4086.47</v>
+        <v>2200.4</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1230848-292-CM25</t>
+          <t>1230848-293-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2200.4</v>
+        <v>4086.47</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3506-746-CM25</t>
+          <t>1057384-730-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2192.85</v>
+        <v>3132.64</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1057384-730-CM25</t>
+          <t>3506-746-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15294,12 +15294,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3132.64</v>
+        <v>2192.85</v>
       </c>
     </row>
     <row r="230">
@@ -15529,7 +15529,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1033-2376-CM25</t>
+          <t>2215-1719-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15554,12 +15554,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15588,13 +15588,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2823.88</v>
+        <v>5229.41</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2215-1719-CM25</t>
+          <t>1033-2376-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15619,12 +15619,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>5229.41</v>
+        <v>2823.88</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>4051-340-CM25</t>
+          <t>1057385-450-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15699,17 +15699,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>7835.77</v>
+        <v>4165.19</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1057385-450-CM25</t>
+          <t>4051-340-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15744,17 +15744,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15764,17 +15764,17 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>4165.19</v>
+        <v>7835.77</v>
       </c>
     </row>
     <row r="237">
@@ -16504,7 +16504,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1233623-874-CM25</t>
+          <t>993-352-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16524,17 +16524,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>42514.75</v>
+        <v>31886.06</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>993-352-CM25</t>
+          <t>1233623-874-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16589,17 +16589,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16628,7 +16628,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>31886.06</v>
+        <v>42514.75</v>
       </c>
     </row>
     <row r="250">
@@ -16894,7 +16894,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1354-76-CM25</t>
+          <t>649-80-CM25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.002.008-9</t>
+          <t>61.930.500-0</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>4321.38</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3146-93-CM25</t>
+          <t>2258-26599-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16979,17 +16979,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3241.04</v>
+        <v>8210.620000000001</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>649-80-CM25</t>
+          <t>3146-93-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17044,17 +17044,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.930.500-0</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2268.73</v>
+        <v>3241.04</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2258-26599-CM25</t>
+          <t>1354-76-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.002.008-9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,7 +17148,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>8210.620000000001</v>
+        <v>4321.38</v>
       </c>
     </row>
     <row r="258">
@@ -17284,7 +17284,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>697036-116-CM25</t>
+          <t>1057384-821-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17304,17 +17304,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17343,7 +17343,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>3805.09</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="261">
@@ -17414,7 +17414,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1057384-821-CM25</t>
+          <t>697036-116-CM25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17434,17 +17434,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17473,7 +17473,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3261.51</v>
+        <v>3805.09</v>
       </c>
     </row>
     <row r="263">
@@ -17544,7 +17544,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1410-1159-CM25</t>
+          <t>2215-1841-CM25</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17569,12 +17569,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17603,13 +17603,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>5905.34</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2215-1841-CM25</t>
+          <t>1410-1159-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>10736.99</v>
+        <v>5905.34</v>
       </c>
     </row>
     <row r="266">
@@ -17999,7 +17999,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3506-909-CM25</t>
+          <t>3506-910-CM25</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18058,13 +18058,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>17238.41</v>
+        <v>2262.54</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3506-910-CM25</t>
+          <t>3506-909-CM25</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18123,7 +18123,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2262.54</v>
+        <v>17238.41</v>
       </c>
     </row>
     <row r="273">
@@ -18259,7 +18259,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1230848-337-CM25</t>
+          <t>1230848-336-CM25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>4214.53</v>
+        <v>2269.36</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1230848-336-CM25</t>
+          <t>1230848-337-CM25</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2269.36</v>
+        <v>4214.53</v>
       </c>
     </row>
     <row r="277">
@@ -18844,7 +18844,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1410-2615-CM25</t>
+          <t>993-402-CM25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18864,17 +18864,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>5464.54</v>
+        <v>36065.97</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>993-402-CM25</t>
+          <t>1410-2615-CM25</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18929,17 +18929,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>36065.97</v>
+        <v>5464.54</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2385-1225-CM25</t>
+          <t>3834-297-CM25</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18994,17 +18994,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19014,17 +19014,17 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>11191.22</v>
+        <v>24178.48</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3834-297-CM25</t>
+          <t>2385-1225-CM25</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19059,17 +19059,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19079,17 +19079,17 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>24178.48</v>
+        <v>11191.22</v>
       </c>
     </row>
     <row r="288">
@@ -19234,7 +19234,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2122-363-CM25</t>
+          <t>3149-468-CM25</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19259,12 +19259,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19293,13 +19293,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>17210.18</v>
+        <v>11032.17</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1775-75-CM25</t>
+          <t>1057384-916-CM25</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19319,17 +19319,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3657.58</v>
+        <v>3309.65</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3149-468-CM25</t>
+          <t>2122-363-CM25</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>11032.17</v>
+        <v>17210.18</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1057384-916-CM25</t>
+          <t>1775-75-CM25</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19449,17 +19449,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19488,7 +19488,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3309.65</v>
+        <v>3657.58</v>
       </c>
     </row>
     <row r="294">
@@ -19819,7 +19819,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1495202-7-CM25</t>
+          <t>1410-2666-CM25</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19844,12 +19844,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19878,13 +19878,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>7133.61</v>
+        <v>2304.7</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1410-2666-CM25</t>
+          <t>1495202-7-CM25</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,7 +19943,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2304.7</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="301">
@@ -20859,7 +20859,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1775-1-CM26</t>
+          <t>3149-15-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20879,17 +20879,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20918,13 +20918,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>5693.4</v>
+        <v>2391.23</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3149-15-CM26</t>
+          <t>1775-1-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20944,17 +20944,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2391.23</v>
+        <v>5693.4</v>
       </c>
     </row>
     <row r="317">
@@ -21509,7 +21509,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>707415-8-CM26</t>
+          <t>2385-49-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21534,12 +21534,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21549,17 +21549,17 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -21568,13 +21568,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>11655.69</v>
+        <v>40212.13</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2385-49-CM26</t>
+          <t>707415-8-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21599,12 +21599,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21614,17 +21614,17 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -21633,7 +21633,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>40212.13</v>
+        <v>11655.69</v>
       </c>
     </row>
     <row r="327">
@@ -21704,7 +21704,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>3506-85-CM26</t>
+          <t>1230848-11-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21763,13 +21763,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2425.87</v>
+        <v>4505.18</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>3506-84-CM26</t>
+          <t>1410-92-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21789,17 +21789,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>20793.14</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="330">
@@ -21899,7 +21899,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1410-92-CM26</t>
+          <t>3506-85-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21919,17 +21919,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21958,13 +21958,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>8086.22</v>
+        <v>2425.87</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1230848-11-CM26</t>
+          <t>3506-84-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21989,12 +21989,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>4505.18</v>
+        <v>20793.14</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1233623-29-CM26</t>
+          <t>1233623-30-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22088,13 +22088,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>17559.26</v>
+        <v>35118.53</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1233623-30-CM26</t>
+          <t>1233623-29-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22153,13 +22153,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>35118.53</v>
+        <v>17559.26</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1216060-31-CM26</t>
+          <t>881-13-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22179,17 +22179,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>65.109.282-5</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes y Recreación Calama</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22218,13 +22218,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>2920.36</v>
+        <v>23362.85</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>881-13-CM26</t>
+          <t>1216060-31-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22244,17 +22244,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>65.109.282-5</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>Corporación Municipal de Deportes y Recreación Calama</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22283,7 +22283,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>23362.85</v>
+        <v>2920.36</v>
       </c>
     </row>
     <row r="337">
@@ -23199,7 +23199,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1057385-73-CM26</t>
+          <t>1983-17-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23224,12 +23224,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>60.701.011-0</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23239,17 +23239,17 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -23258,13 +23258,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>4399.91</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1983-17-CM26</t>
+          <t>1057385-73-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23289,12 +23289,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>60.701.011-0</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23304,17 +23304,17 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -23323,7 +23323,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2309.95</v>
+        <v>4399.91</v>
       </c>
     </row>
     <row r="353">
@@ -23394,7 +23394,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4051-41-CM26</t>
+          <t>3916-122-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23419,12 +23419,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -23453,7 +23453,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>7856.12</v>
+        <v>17535.94</v>
       </c>
     </row>
     <row r="355">
@@ -23524,7 +23524,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>3916-122-CM26</t>
+          <t>4051-41-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>17535.94</v>
+        <v>7856.12</v>
       </c>
     </row>
     <row r="357">
@@ -23654,7 +23654,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>3149-85-CM26</t>
+          <t>1747-56-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23674,17 +23674,17 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.606.205-0</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>HOSPITAL DE MEJILLONES</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>10927.17</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1057384-261-CM26</t>
+          <t>3149-85-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23739,17 +23739,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>3824.51</v>
+        <v>10927.17</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>650-23-CM26</t>
+          <t>1057384-261-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23843,13 +23843,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2291.43</v>
+        <v>3824.51</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1747-56-CM26</t>
+          <t>650-23-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23874,12 +23874,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.606.205-0</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>HOSPITAL DE MEJILLONES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23908,7 +23908,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2294.71</v>
+        <v>2291.43</v>
       </c>
     </row>
     <row r="362">
@@ -24174,7 +24174,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1354-7-CM26</t>
+          <t>3858-146-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24199,12 +24199,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>61.002.008-9</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24233,13 +24233,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2695.53</v>
+        <v>5391.07</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>3858-146-CM26</t>
+          <t>1354-7-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24264,12 +24264,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.002.008-9</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>5391.07</v>
+        <v>2695.53</v>
       </c>
     </row>
     <row r="368">
@@ -24434,7 +24434,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>4291-283-CM26</t>
+          <t>3506-232-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24459,12 +24459,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24493,13 +24493,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>5421.99</v>
+        <v>23314.57</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>3506-232-CM26</t>
+          <t>1346284-76-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24519,17 +24519,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24539,17 +24539,17 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>23314.57</v>
+        <v>4402.66</v>
       </c>
     </row>
     <row r="372">
@@ -24629,7 +24629,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1346284-76-CM26</t>
+          <t>4291-283-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24649,17 +24649,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24669,17 +24669,17 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -24688,7 +24688,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>4402.66</v>
+        <v>5421.99</v>
       </c>
     </row>
     <row r="374">
@@ -25409,7 +25409,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2258-3143-CM26</t>
+          <t>2215-465-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25434,12 +25434,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25468,13 +25468,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>7446.52</v>
+        <v>5641.3</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2215-465-CM26</t>
+          <t>2258-3143-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25499,12 +25499,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25533,7 +25533,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>5641.3</v>
+        <v>7446.52</v>
       </c>
     </row>
     <row r="387">
@@ -25864,7 +25864,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>769-255-CM26</t>
+          <t>1287083-18-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25889,12 +25889,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>65.082.914-k</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>Corporacion Municipal de Deportes y Recreación de la comuna de San Pedro de Atacama</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25923,7 +25923,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>44689.24</v>
+        <v>3351.69</v>
       </c>
     </row>
     <row r="393">
@@ -25994,7 +25994,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1287083-18-CM26</t>
+          <t>769-255-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -26019,12 +26019,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>65.082.914-k</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Corporacion Municipal de Deportes y Recreación de la comuna de San Pedro de Atacama</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -26053,7 +26053,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3351.69</v>
+        <v>44689.24</v>
       </c>
     </row>
     <row r="395">
@@ -26644,7 +26644,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1057385-140-CM26</t>
+          <t>4051-90-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26669,12 +26669,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26684,17 +26684,17 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -26703,13 +26703,13 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>4473.02</v>
+        <v>12477.5</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>4051-90-CM26</t>
+          <t>1057385-140-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26734,12 +26734,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26749,17 +26749,17 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -26768,13 +26768,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>12477.5</v>
+        <v>4473.02</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>3506-336-CM26</t>
+          <t>2215-592-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26794,17 +26794,17 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26833,7 +26833,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>3667.03</v>
+        <v>11112.22</v>
       </c>
     </row>
     <row r="407">
@@ -26904,7 +26904,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2215-592-CM26</t>
+          <t>3506-336-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26924,17 +26924,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26963,7 +26963,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>11112.22</v>
+        <v>3667.03</v>
       </c>
     </row>
     <row r="409">
@@ -27099,7 +27099,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1230848-85-CM26</t>
+          <t>838098-24-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -27119,17 +27119,17 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -27139,17 +27139,17 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -27158,13 +27158,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>5545.76</v>
+        <v>2440.13</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>838098-24-CM26</t>
+          <t>1410-414-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27189,12 +27189,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27204,17 +27204,17 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -27223,13 +27223,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2440.13</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1410-414-CM26</t>
+          <t>1230848-85-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27249,17 +27249,17 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27814,7 +27814,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>904669-3-CM26</t>
+          <t>1057384-443-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27839,12 +27839,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>60.804.003-k</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -27873,7 +27873,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>2983.5</v>
+        <v>6719.6</v>
       </c>
     </row>
     <row r="423">
@@ -27944,7 +27944,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1057384-443-CM26</t>
+          <t>3149-154-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27969,12 +27969,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -28003,13 +28003,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>6719.6</v>
+        <v>16799.01</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>4051-108-CM26</t>
+          <t>904669-3-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28034,12 +28034,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>60.804.003-k</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -28068,13 +28068,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>11994.49</v>
+        <v>2983.5</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>3149-154-CM26</t>
+          <t>4051-108-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -28099,12 +28099,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -28133,7 +28133,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>16799.01</v>
+        <v>11994.49</v>
       </c>
     </row>
     <row r="427">
@@ -29439,7 +29439,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>1747-125-CM26</t>
+          <t>1401-29-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -29464,12 +29464,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>61.606.205-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>HOSPITAL DE MEJILLONES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -29498,13 +29498,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2328.12</v>
+        <v>4573.65</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>4468-93-CM26</t>
+          <t>1775-38-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29524,17 +29524,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>38801.85</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>1775-38-CM26</t>
+          <t>1747-125-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29594,12 +29594,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>61.606.205-0</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>HOSPITAL DE MEJILLONES</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -29628,13 +29628,13 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>10852.81</v>
+        <v>2328.12</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>1401-29-CM26</t>
+          <t>4468-93-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -29654,17 +29654,17 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -29693,13 +29693,13 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>4573.65</v>
+        <v>38801.85</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1158-72-CM26</t>
+          <t>3506-472-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -29724,12 +29724,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -29758,13 +29758,13 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>5518.17</v>
+        <v>23446.79</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>3506-472-CM26</t>
+          <t>3506-473-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>23446.79</v>
+        <v>3598.81</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>3506-473-CM26</t>
+          <t>1057384-522-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29849,17 +29849,17 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -29888,13 +29888,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>3598.81</v>
+        <v>6543.29</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1057384-522-CM26</t>
+          <t>1158-72-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29914,17 +29914,17 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29953,7 +29953,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>6543.29</v>
+        <v>5518.17</v>
       </c>
     </row>
     <row r="455">
@@ -30284,7 +30284,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>1410-585-CM26</t>
+          <t>1057385-190-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -30309,12 +30309,12 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -30324,17 +30324,17 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -30343,13 +30343,13 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>8626.73</v>
+        <v>5391.71</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>1057385-190-CM26</t>
+          <t>1410-585-CM26</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -30374,12 +30374,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -30389,17 +30389,17 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>5391.71</v>
+        <v>8626.73</v>
       </c>
     </row>
     <row r="462">
@@ -30999,7 +30999,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>3506-526-CM26</t>
+          <t>3149-216-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -31019,17 +31019,17 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -31058,13 +31058,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>3552.82</v>
+        <v>16149.18</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>3149-216-CM26</t>
+          <t>3506-526-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -31084,17 +31084,17 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -31123,7 +31123,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>16149.18</v>
+        <v>3552.82</v>
       </c>
     </row>
     <row r="473">
@@ -31649,7 +31649,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>1057385-237-CM26</t>
+          <t>3506-581-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -31669,17 +31669,17 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -31689,17 +31689,17 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -31708,13 +31708,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>4308.39</v>
+        <v>28543.12</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>3506-581-CM26</t>
+          <t>1057385-237-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -31734,17 +31734,17 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -31754,17 +31754,17 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -31773,7 +31773,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>28543.12</v>
+        <v>4308.39</v>
       </c>
     </row>
     <row r="483">
@@ -32234,7 +32234,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>4051-157-CM26</t>
+          <t>1410-743-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -32259,12 +32259,12 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -32293,13 +32293,13 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>14166.67</v>
+        <v>8881.58</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>1410-743-CM26</t>
+          <t>4051-157-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -32324,12 +32324,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -32358,7 +32358,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>8881.58</v>
+        <v>14166.67</v>
       </c>
     </row>
     <row r="492">
@@ -32949,7 +32949,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1410-793-CM26</t>
+          <t>2258-6867-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32974,12 +32974,12 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -33008,13 +33008,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>6583.06</v>
+        <v>6775.07</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1775-50-CM26</t>
+          <t>4051-172-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -33039,12 +33039,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -33073,7 +33073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>10971.77</v>
+        <v>15217.84</v>
       </c>
     </row>
     <row r="503">
@@ -33144,7 +33144,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>4051-172-CM26</t>
+          <t>1775-50-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -33169,12 +33169,12 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -33203,13 +33203,13 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>15217.84</v>
+        <v>10971.77</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2258-6867-CM26</t>
+          <t>1410-793-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -33234,12 +33234,12 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -33268,7 +33268,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>6775.07</v>
+        <v>6583.06</v>
       </c>
     </row>
     <row r="506">
@@ -33599,7 +33599,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2385-695-CM26</t>
+          <t>1057384-731-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33619,17 +33619,17 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -33639,17 +33639,17 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
@@ -33658,13 +33658,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>3213.82</v>
+        <v>3295.43</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1057384-731-CM26</t>
+          <t>1057385-314-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -33689,12 +33689,12 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -33704,17 +33704,17 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -33723,13 +33723,13 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>3295.43</v>
+        <v>5356.36</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>1410-838-CM26</t>
+          <t>2385-695-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33754,12 +33754,12 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -33769,17 +33769,17 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -33788,13 +33788,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>7338.21</v>
+        <v>3213.82</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2385-689-CM26</t>
+          <t>1287083-55-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33814,17 +33814,17 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>65.082.914-k</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Corporacion Municipal de Deportes y Recreación de la comuna de San Pedro de Atacama</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -33834,17 +33834,17 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
@@ -33853,13 +33853,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>37494.51</v>
+        <v>2356.8</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>1287083-55-CM26</t>
+          <t>1410-838-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33884,12 +33884,12 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>65.082.914-k</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Corporacion Municipal de Deportes y Recreación de la comuna de San Pedro de Atacama</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -33918,13 +33918,13 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2356.8</v>
+        <v>7338.21</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>1057385-314-CM26</t>
+          <t>2385-689-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33949,12 +33949,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -33983,7 +33983,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>5356.36</v>
+        <v>37494.51</v>
       </c>
     </row>
     <row r="517">
@@ -34509,7 +34509,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2215-1014-CM26</t>
+          <t>3506-704-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -34534,12 +34534,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -34568,13 +34568,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>10443.54</v>
+        <v>4888.88</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>769-666-CM26</t>
+          <t>2215-1014-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -34594,17 +34594,17 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -34633,13 +34633,13 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>62661.22</v>
+        <v>10443.54</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>1410-869-CM26</t>
+          <t>769-666-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34659,17 +34659,17 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -34698,13 +34698,13 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>8354.83</v>
+        <v>62661.22</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>3916-384-CM26</t>
+          <t>1410-869-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34719,7 +34719,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -34729,12 +34729,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -34763,13 +34763,13 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>17824.3</v>
+        <v>8354.83</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>4468-124-CM26</t>
+          <t>3916-384-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34784,22 +34784,22 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -34828,13 +34828,13 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>12148.51</v>
+        <v>17824.3</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>4051-196-CM26</t>
+          <t>4468-124-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34849,7 +34849,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -34859,12 +34859,12 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -34893,13 +34893,13 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>15410.78</v>
+        <v>12148.51</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>3834-333-CM26</t>
+          <t>1057384-782-CM26</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -34919,17 +34919,17 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -34958,13 +34958,13 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>16694.14</v>
+        <v>3130.15</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>1057384-782-CM26</t>
+          <t>4051-196-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -34984,17 +34984,17 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -35023,13 +35023,13 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>3130.15</v>
+        <v>15410.78</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>1230848-189-CM26</t>
+          <t>3834-333-CM26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -35044,7 +35044,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -35054,12 +35054,12 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -35088,13 +35088,13 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>7296.3</v>
+        <v>16694.14</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>993-225-CM26</t>
+          <t>1230848-189-CM26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -35109,7 +35109,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -35119,12 +35119,12 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -35153,7 +35153,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>31065.23</v>
+        <v>7296.3</v>
       </c>
     </row>
     <row r="535">
@@ -35224,7 +35224,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>1410-909-CM26</t>
+          <t>993-225-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -35239,7 +35239,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -35249,12 +35249,12 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -35283,7 +35283,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>7241.47</v>
+        <v>31065.23</v>
       </c>
     </row>
     <row r="537">
@@ -35349,6 +35349,1631 @@
       </c>
       <c r="M537" s="2" t="n">
         <v>3550.91</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>1410-909-CM26</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M538" s="2" t="n">
+        <v>7241.47</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>1057384-794-CM26</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>61.606.203-4</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M539" s="2" t="n">
+        <v>4766.44</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>1033-64-CM26</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M540" s="2" t="n">
+        <v>12133.07</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>1354-35-CM26</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>61.002.008-9</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M541" s="2" t="n">
+        <v>2570.43</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>1077908-172-CM26</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>62.000.380-8</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M542" s="2" t="n">
+        <v>4319.81</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>1057384-796-CM26</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>61.606.203-4</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M543" s="2" t="n">
+        <v>3049.28</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>1057385-372-CM26</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M544" s="2" t="n">
+        <v>5077.07</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>3506-749-CM26</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M545" s="2" t="n">
+        <v>21831.4</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>1997-61-CM26</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>60.511.023-1</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M546" s="2" t="n">
+        <v>2251.22</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2385-777-CM26</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M547" s="2" t="n">
+        <v>35814.79</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>838098-48-CM26</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>73.923.800-5</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>79.588.870-5</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M548" s="2" t="n">
+        <v>3203.17</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>4468-132-CM26</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M549" s="2" t="n">
+        <v>21393.43</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>3506-769-CM26</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M550" s="2" t="n">
+        <v>3361.82</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>1999-85-CM26</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>60.103.001-2</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M551" s="2" t="n">
+        <v>2241.22</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>707415-112-CM26</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M552" s="2" t="n">
+        <v>4189.62</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>650-136-CM26</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>61.814.000-8</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M553" s="2" t="n">
+        <v>5109.29</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>1057384-819-CM26</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>61.606.203-4</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M554" s="2" t="n">
+        <v>3039.42</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>3916-416-CM26</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M555" s="2" t="n">
+        <v>17463.5</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>1230848-224-CM26</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>70.954.900-6</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M556" s="2" t="n">
+        <v>7130.85</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>3146-70-CM26</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M557" s="2" t="n">
+        <v>3055.43</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>904669-9-CM26</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>60.804.003-k</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M558" s="2" t="n">
+        <v>2291.57</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>1158-122-CM26</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M559" s="2" t="n">
+        <v>3035.07</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>3149-337-CM26</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M560" s="2" t="n">
+        <v>15355.95</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>1057384-865-CM26</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>61.606.203-4</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M561" s="2" t="n">
+        <v>4054.41</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>1410-996-CM26</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M562" s="2" t="n">
+        <v>8108.82</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/antofagasta.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/antofagasta.xlsx
@@ -36934,7 +36934,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
